--- a/KatalonData/IWPBootstrapData/VRelayPaymentsCC_27.xlsx
+++ b/KatalonData/IWPBootstrapData/VRelayPaymentsCC_27.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="188">
   <si>
     <t>Result</t>
   </si>
@@ -471,6 +471,144 @@
   </si>
   <si>
     <t>Fri Jul 31 20:06:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 11 19:50:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 11 20:02:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 22:37:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 22:49:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 22:58:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:03:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:08:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:13:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:14:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:24:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:30:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:35:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:41:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:48:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:54:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 00:00:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 00:04:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 00:09:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 00:13:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 00:18:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 00:22:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 00:27:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 00:31:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 18:09:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 18:31:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 19:16:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 01:33:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 01:45:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 01:54:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:00:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:04:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:09:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:10:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:19:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:24:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:30:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:36:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:48:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:55:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:58:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 03:03:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 03:09:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 03:14:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 03:19:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 03:24:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 03:28:34 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -860,7 +998,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>115</v>
+        <v>174</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -954,7 +1092,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1048,7 +1186,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>121</v>
+        <v>180</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1145,7 +1283,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1241,7 +1379,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>133</v>
+        <v>169</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1333,7 +1471,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>136</v>
+        <v>177</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1425,7 +1563,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>119</v>
+        <v>178</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1520,7 +1658,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1619,7 +1757,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>123</v>
+        <v>182</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1715,7 +1853,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1807,7 +1945,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>138</v>
+        <v>179</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1896,10 +2034,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>112</v>
+        <v>171</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1999,7 +2137,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2098,7 +2236,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>125</v>
+        <v>184</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2194,7 +2332,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>127</v>
+        <v>186</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2461,10 +2599,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2556,7 +2694,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>117</v>
+        <v>176</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2648,7 +2786,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2742,7 +2880,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>128</v>
+        <v>187</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/IWPBootstrapData/VRelayPaymentsCC_27.xlsx
+++ b/KatalonData/IWPBootstrapData/VRelayPaymentsCC_27.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="252">
   <si>
     <t>Result</t>
   </si>
@@ -609,6 +609,198 @@
   </si>
   <si>
     <t>Thu Aug 20 03:28:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:13:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:24:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:32:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:37:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:42:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:47:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:48:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:57:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:01:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:06:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:11:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:17:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:23:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:29:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:31:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:35:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:39:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:44:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:48:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:52:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:56:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 21:29:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 21:33:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 21:36:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 15:46:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 15:59:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:11:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:19:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:24:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:30:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:32:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:43:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:49:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:55:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 17:10:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 17:48:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 18:10:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 18:24:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 18:29:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 18:35:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 18:40:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 18:45:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 18:50:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 18:55:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 00:40:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 00:52:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:02:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:09:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:13:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:21:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:23:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:33:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:39:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:45:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 02:00:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 02:19:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 02:25:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 02:29:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 02:33:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 02:39:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 02:43:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 02:48:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 02:55:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 03:01:00 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -995,10 +1187,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1092,7 +1284,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>170</v>
+        <v>234</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1183,10 +1375,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>180</v>
+        <v>244</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1283,7 +1475,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>168</v>
+        <v>232</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1379,7 +1571,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>169</v>
+        <v>233</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1468,10 +1660,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>177</v>
+        <v>241</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1560,10 +1752,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>178</v>
+        <v>222</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1658,7 +1850,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>181</v>
+        <v>245</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1757,7 +1949,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>182</v>
+        <v>246</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1850,10 +2042,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>155</v>
+        <v>242</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1945,7 +2137,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>179</v>
+        <v>243</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2034,10 +2226,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>171</v>
+        <v>235</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2137,7 +2329,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>183</v>
+        <v>247</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2236,7 +2428,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>184</v>
+        <v>248</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2329,10 +2521,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>186</v>
+        <v>250</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2602,7 +2794,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>175</v>
+        <v>239</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2691,10 +2883,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>176</v>
+        <v>240</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2786,7 +2978,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>172</v>
+        <v>236</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2880,7 +3072,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>187</v>
+        <v>251</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/IWPBootstrapData/VRelayPaymentsCC_27.xlsx
+++ b/KatalonData/IWPBootstrapData/VRelayPaymentsCC_27.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="273">
   <si>
     <t>Result</t>
   </si>
@@ -801,6 +801,69 @@
   </si>
   <si>
     <t>Fri Oct 23 03:01:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 00:35:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 00:48:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 00:58:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:04:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:09:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:14:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:16:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:27:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:33:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:40:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:47:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:54:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 02:00:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 02:07:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 02:11:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 02:15:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 02:19:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 02:24:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 02:30:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 02:34:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 02:39:44 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1190,7 +1253,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1281,10 +1344,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1375,10 +1438,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1475,7 +1538,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1571,7 +1634,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1660,10 +1723,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1752,10 +1815,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>222</v>
+        <v>262</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1850,7 +1913,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1949,7 +2012,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2045,7 +2108,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2134,10 +2197,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2229,7 +2292,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2329,7 +2392,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2428,7 +2491,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2521,10 +2584,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2791,10 +2854,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2883,10 +2946,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2978,7 +3041,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3072,7 +3135,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
